--- a/books.xlsx
+++ b/books.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9000"/>
+    <workbookView windowWidth="11520" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,148 +38,148 @@
     <t>Cover</t>
   </si>
   <si>
+    <t>This Woven Kingdom</t>
+  </si>
+  <si>
     <t>Taheren Mafi</t>
   </si>
   <si>
-    <t>This Woven Kingdom</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg</t>
   </si>
   <si>
-    <t>Kylie Snow</t>
-  </si>
-  <si>
-    <t>The Lies of Lena</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1708376993i/208884873.jpg</t>
-  </si>
-  <si>
-    <t>Dani Francis</t>
-  </si>
-  <si>
-    <t>Silver Elite</t>
-  </si>
-  <si>
-    <t>https://images-na.ssl-images-amazon.com/images/S/compressed.photo.goodreads.com/books/1728609987i/217245572.jpg</t>
+    <t>Wild Reverence</t>
+  </si>
+  <si>
+    <t>Rebecca Ross</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg</t>
+  </si>
+  <si>
+    <t>The Bloody Branch</t>
+  </si>
+  <si>
+    <t>Brigid Lowe</t>
+  </si>
+  <si>
+    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
+  </si>
+  <si>
+    <t>The Serpent and the Wolf</t>
   </si>
   <si>
     <t>Rebecca Robinson</t>
   </si>
   <si>
-    <t>The Serpent and the Wolf</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg</t>
   </si>
   <si>
+    <t>Shield of Sparrows</t>
+  </si>
+  <si>
     <t>Devney Perry</t>
   </si>
   <si>
-    <t>Shield of Sparrows</t>
-  </si>
-  <si>
     <t>https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg</t>
   </si>
   <si>
-    <t>Brandon Sanderson</t>
-  </si>
-  <si>
-    <t>Mistborn: The Final Empire</t>
-  </si>
-  <si>
-    <t>https://cdn.kobo.com/book-images/262e58e4-8ab1-4ab4-b89a-eac880b1a0a1/1200/1200/False/mistborn.jpg</t>
+    <t>A Fate Forged in Fire</t>
   </si>
   <si>
     <t>Hazel McBride</t>
   </si>
   <si>
-    <t>A Fate Forged in Fire</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg</t>
   </si>
   <si>
+    <t>City of Stairs</t>
+  </si>
+  <si>
     <t>R. J. Bennett</t>
   </si>
   <si>
-    <t>City of Stairs</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg</t>
   </si>
   <si>
+    <t>Red Rising</t>
+  </si>
+  <si>
     <t>Pierce Brown</t>
   </si>
   <si>
-    <t>Red Rising</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg</t>
   </si>
   <si>
+    <t>The Second Death of Locke</t>
+  </si>
+  <si>
     <t>V. L. Bovalino</t>
   </si>
   <si>
-    <t>The Second Death of Locke</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
   </si>
   <si>
+    <t>Masters of Death</t>
+  </si>
+  <si>
     <t>Olivie Blake</t>
   </si>
   <si>
-    <t>Masters of Death</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg</t>
   </si>
   <si>
-    <t>Invi Wright</t>
-  </si>
-  <si>
-    <t>The Female</t>
-  </si>
-  <si>
-    <t>https://api.bruna.nl/images/active/carrousel/fullsize/9781966285007_front.jpg</t>
-  </si>
-  <si>
-    <t>Ali Hazelwood</t>
-  </si>
-  <si>
-    <t>Bride</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1730451646i/181344829.jpg</t>
-  </si>
-  <si>
-    <t>Erin Sterling</t>
-  </si>
-  <si>
-    <t>The Ex Hex</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1619305366i/56554626.jpg</t>
-  </si>
-  <si>
-    <t>RuNyx</t>
-  </si>
-  <si>
-    <t>Enigma</t>
-  </si>
-  <si>
-    <t>https://mpd-biblio-covers.imgix.net/9781250334244.jpg?w=300&amp;dpr=3</t>
+    <t>The Fifth Season</t>
+  </si>
+  <si>
+    <t>N. K. Jemisin</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/The_Fifth_Season_%28novel%29#/media/File%3AThe_Fifth_Season_(novel).jpg</t>
+  </si>
+  <si>
+    <t>The Wolf King</t>
+  </si>
+  <si>
+    <t>Lauren Palphreyman</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
+  </si>
+  <si>
+    <t>Smoke and Scar</t>
+  </si>
+  <si>
+    <t>Gretchen Powell</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
+  </si>
+  <si>
+    <t>Tusk Love</t>
   </si>
   <si>
     <t>Thea Guanzon</t>
   </si>
   <si>
-    <t>Tusk Love</t>
-  </si>
-  <si>
     <t>https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1</t>
+  </si>
+  <si>
+    <t>Son of the morning</t>
+  </si>
+  <si>
+    <t>Awaeke Emezi</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg</t>
+  </si>
+  <si>
+    <t>the adventures of Amin al-sirafi</t>
+  </si>
+  <si>
+    <t>S A Chakraborty</t>
+  </si>
+  <si>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10</t>
   </si>
 </sst>
 </file>
@@ -192,7 +192,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -228,12 +228,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1E1915"/>
-      <name val="Copernicus"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -378,7 +372,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -388,6 +382,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -719,137 +719,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -865,7 +865,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1431,25 +1440,25 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="53.55" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="40.35" spans="1:3">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="53.55" spans="1:3">
+    <row r="4" ht="40.35" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -1475,7 +1484,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="53.55" spans="1:3">
+    <row r="7" ht="40.35" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
@@ -1541,14 +1550,14 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="27.15" spans="1:3">
+    <row r="13" ht="40.35" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1563,14 +1572,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="53.55" spans="1:3">
+    <row r="15" ht="40.35" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="6" t="s">
         <v>44</v>
       </c>
     </row>
@@ -1585,7 +1594,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="40.35" spans="1:3">
+    <row r="17" ht="53.55" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>48</v>
       </c>
@@ -1597,25 +1606,28 @@
       </c>
     </row>
     <row r="18" ht="15.15" spans="1:3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="2"/>
-      <c r="C18" s="3"/>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg"/>
-    <hyperlink ref="C4" r:id="rId2" display="https://images-na.ssl-images-amazon.com/images/S/compressed.photo.goodreads.com/books/1728609987i/217245572.jpg" tooltip="https://images-na.ssl-images-amazon.com/images/S/compressed.photo.goodreads.com/books/1728609987i/217245572.jpg"/>
-    <hyperlink ref="C5" r:id="rId3" display="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg" tooltip="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg"/>
-    <hyperlink ref="C6" r:id="rId4" display="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg" tooltip="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://cdn.kobo.com/book-images/262e58e4-8ab1-4ab4-b89a-eac880b1a0a1/1200/1200/False/mistborn.jpg" tooltip="https://cdn.kobo.com/book-images/262e58e4-8ab1-4ab4-b89a-eac880b1a0a1/1200/1200/False/mistborn.jpg"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg"/>
-    <hyperlink ref="C9" r:id="rId7" display="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg" tooltip="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg"/>
-    <hyperlink ref="C10" r:id="rId8" display="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg"/>
-    <hyperlink ref="C11" r:id="rId9" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C12" r:id="rId10" display="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C13" r:id="rId11" display="https://api.bruna.nl/images/active/carrousel/fullsize/9781966285007_front.jpg" tooltip="https://api.bruna.nl/images/active/carrousel/fullsize/9781966285007_front.jpg"/>
-    <hyperlink ref="C16" r:id="rId12" display="https://mpd-biblio-covers.imgix.net/9781250334244.jpg?w=300&amp;dpr=3" tooltip="https://mpd-biblio-covers.imgix.net/9781250334244.jpg?w=300&amp;dpr=3"/>
-    <hyperlink ref="C17" r:id="rId13" display="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1" tooltip="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg" tooltip="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg"/>
+    <hyperlink ref="C4" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg" tooltip="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg" tooltip="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg"/>
+    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg" tooltip="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg"/>
+    <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C12" r:id="rId11" display="https://en.wikipedia.org/wiki/The_Fifth_Season_%28novel%29#/media/File%3AThe_Fifth_Season_(novel).jpg"/>
+    <hyperlink ref="C13" r:id="rId12" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
+    <hyperlink ref="C14" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
+    <hyperlink ref="C15" r:id="rId14" display="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1" tooltip="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1"/>
+    <hyperlink ref="C16" r:id="rId15" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
+    <hyperlink ref="C17" r:id="rId16" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11520" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="8280"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -65,49 +65,40 @@
     <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
   </si>
   <si>
-    <t>The Serpent and the Wolf</t>
-  </si>
-  <si>
-    <t>Rebecca Robinson</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg</t>
-  </si>
-  <si>
-    <t>Shield of Sparrows</t>
-  </si>
-  <si>
-    <t>Devney Perry</t>
-  </si>
-  <si>
-    <t>https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg</t>
-  </si>
-  <si>
-    <t>A Fate Forged in Fire</t>
-  </si>
-  <si>
-    <t>Hazel McBride</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>City of Stairs</t>
-  </si>
-  <si>
-    <t>R. J. Bennett</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg</t>
-  </si>
-  <si>
-    <t>Red Rising</t>
-  </si>
-  <si>
-    <t>Pierce Brown</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg</t>
+    <t>Jade Fire Gold</t>
+  </si>
+  <si>
+    <t>June CL Tan</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
+  </si>
+  <si>
+    <t>His Majesty's Dragon</t>
+  </si>
+  <si>
+    <t>Naomi Novik</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg</t>
+  </si>
+  <si>
+    <t>The Tainted Cup</t>
+  </si>
+  <si>
+    <t>Robert Jackson Bennet</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>The Everlasting</t>
+  </si>
+  <si>
+    <t>Alix E. Harrow</t>
+  </si>
+  <si>
+    <t>https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg</t>
   </si>
   <si>
     <t>The Second Death of Locke</t>
@@ -134,7 +125,7 @@
     <t>N. K. Jemisin</t>
   </si>
   <si>
-    <t>https://en.wikipedia.org/wiki/The_Fifth_Season_%28novel%29#/media/File%3AThe_Fifth_Season_(novel).jpg</t>
+    <t>https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg</t>
   </si>
   <si>
     <t>The Wolf King</t>
@@ -155,15 +146,6 @@
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
   </si>
   <si>
-    <t>Tusk Love</t>
-  </si>
-  <si>
-    <t>Thea Guanzon</t>
-  </si>
-  <si>
-    <t>https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1</t>
-  </si>
-  <si>
     <t>Son of the morning</t>
   </si>
   <si>
@@ -173,13 +155,31 @@
     <t>https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg</t>
   </si>
   <si>
-    <t>the adventures of Amin al-sirafi</t>
+    <t>The Adventures of Amina Al-Sirafi</t>
   </si>
   <si>
     <t>S A Chakraborty</t>
   </si>
   <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10</t>
+  </si>
+  <si>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
+  </si>
+  <si>
+    <t>A Fate Inked in Blood</t>
+  </si>
+  <si>
+    <t>Danielle L. Jensen</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg</t>
   </si>
 </sst>
 </file>
@@ -849,7 +849,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -866,15 +866,6 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1410,7 +1401,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
@@ -1462,7 +1453,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="40.35" spans="1:3">
+    <row r="5" ht="53.55" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
@@ -1473,7 +1464,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="40.35" spans="1:3">
+    <row r="6" ht="27.15" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1495,7 +1486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="40.35" spans="1:3">
+    <row r="8" ht="53.55" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
@@ -1535,7 +1526,7 @@
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1546,22 +1537,22 @@
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="40.35" spans="1:3">
+    <row r="13" ht="53.55" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="53.55" spans="1:3">
+    <row r="14" ht="40.35" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -1572,18 +1563,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" ht="40.35" spans="1:3">
+    <row r="15" ht="53.55" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="40.35" spans="1:3">
+    <row r="16" ht="53.55" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1604,30 +1595,25 @@
       <c r="C17" s="3" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="18" ht="15.15" spans="1:3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg"/>
     <hyperlink ref="C3" r:id="rId2" display="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg" tooltip="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg"/>
     <hyperlink ref="C4" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg" tooltip="https://m.media-amazon.com/images/I/7186YNOq9wL._SY466_.jpg"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg" tooltip="https://devneyperry.com/wp-content/uploads/2024/11/ShieldOfSparrows-1600-1.jpg"/>
-    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/91E0OEUccOL._UF1000,1000_QL80_.jpg"/>
-    <hyperlink ref="C8" r:id="rId7" display="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg" tooltip="https://media.s-bol.com/JkE8nB1gOpr9/mZ8qPNp/546x840.jpg"/>
-    <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81YOu17CxTL._UF1000,1000_QL80_.jpg"/>
-    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C11" r:id="rId10" display="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C12" r:id="rId11" display="https://en.wikipedia.org/wiki/The_Fifth_Season_%28novel%29#/media/File%3AThe_Fifth_Season_(novel).jpg"/>
-    <hyperlink ref="C13" r:id="rId12" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C14" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
-    <hyperlink ref="C15" r:id="rId14" display="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1" tooltip="https://i0.wp.com/thenerddaily.com/wp-content/uploads/2025/07/Tusk-Love-by-Thea-Guanzon.jpg?w=964&amp;ssl=1"/>
-    <hyperlink ref="C16" r:id="rId15" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
-    <hyperlink ref="C17" r:id="rId16" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg"/>
+    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg" tooltip="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg"/>
+    <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
+    <hyperlink ref="C12" r:id="rId11" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
+    <hyperlink ref="C13" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
+    <hyperlink ref="C14" r:id="rId13" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
+    <hyperlink ref="C15" r:id="rId14" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
+    <hyperlink ref="C16" r:id="rId15" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C17" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="8280"/>
+    <workbookView windowWidth="23040" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t>Title</t>
   </si>
@@ -38,148 +38,139 @@
     <t>Cover</t>
   </si>
   <si>
+    <t>Taheren Mafi</t>
+  </si>
+  <si>
     <t>This Woven Kingdom</t>
   </si>
   <si>
-    <t>Taheren Mafi</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg</t>
   </si>
   <si>
+    <t>Rebecca Ross</t>
+  </si>
+  <si>
     <t>Wild Reverence</t>
   </si>
   <si>
-    <t>Rebecca Ross</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg</t>
   </si>
   <si>
+    <t>Brigid Lowe</t>
+  </si>
+  <si>
     <t>The Bloody Branch</t>
   </si>
   <si>
-    <t>Brigid Lowe</t>
-  </si>
-  <si>
     <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
   </si>
   <si>
+    <t>June CL Tan</t>
+  </si>
+  <si>
     <t>Jade Fire Gold</t>
   </si>
   <si>
-    <t>June CL Tan</t>
-  </si>
-  <si>
     <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
   </si>
   <si>
+    <t>Naomi Novik</t>
+  </si>
+  <si>
     <t>His Majesty's Dragon</t>
   </si>
   <si>
-    <t>Naomi Novik</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg</t>
   </si>
   <si>
+    <t>Robert Jackson Bennet</t>
+  </si>
+  <si>
     <t>The Tainted Cup</t>
   </si>
   <si>
-    <t>Robert Jackson Bennet</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg</t>
   </si>
   <si>
+    <t>Alix E. Harrow</t>
+  </si>
+  <si>
     <t>The Everlasting</t>
   </si>
   <si>
-    <t>Alix E. Harrow</t>
-  </si>
-  <si>
     <t>https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg</t>
   </si>
   <si>
+    <t>V. L. Bovalino</t>
+  </si>
+  <si>
     <t>The Second Death of Locke</t>
   </si>
   <si>
-    <t>V. L. Bovalino</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
   </si>
   <si>
-    <t>Masters of Death</t>
-  </si>
-  <si>
-    <t>Olivie Blake</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg</t>
+    <t>N. K. Jemisin</t>
   </si>
   <si>
     <t>The Fifth Season</t>
   </si>
   <si>
-    <t>N. K. Jemisin</t>
-  </si>
-  <si>
     <t>https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg</t>
   </si>
   <si>
+    <t>Lauren Palphreyman</t>
+  </si>
+  <si>
     <t>The Wolf King</t>
   </si>
   <si>
-    <t>Lauren Palphreyman</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
   </si>
   <si>
+    <t>Gretchen Powell</t>
+  </si>
+  <si>
     <t>Smoke and Scar</t>
   </si>
   <si>
-    <t>Gretchen Powell</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
   </si>
   <si>
+    <t>Awaeke Emezi</t>
+  </si>
+  <si>
     <t>Son of the morning</t>
   </si>
   <si>
-    <t>Awaeke Emezi</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg</t>
   </si>
   <si>
+    <t>S A Chakraborty</t>
+  </si>
+  <si>
     <t>The Adventures of Amina Al-Sirafi</t>
   </si>
   <si>
-    <t>S A Chakraborty</t>
-  </si>
-  <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10</t>
   </si>
   <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
     <t>The Scattered Bones</t>
   </si>
   <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
   </si>
   <si>
-    <t>A Fate Inked in Blood</t>
-  </si>
-  <si>
-    <t>Danielle L. Jensen</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg</t>
+    <t>Shannon J. Spann</t>
+  </si>
+  <si>
+    <t>A Stage Set for Villains</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg</t>
   </si>
 </sst>
 </file>
@@ -849,7 +840,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -866,6 +857,12 @@
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1432,10 +1429,10 @@
       </c>
     </row>
     <row r="3" ht="40.35" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -1515,7 +1512,7 @@
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1530,18 +1527,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="40.35" spans="1:3">
+    <row r="12" ht="53.55" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="53.55" spans="1:3">
+    <row r="13" ht="40.35" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
@@ -1552,7 +1549,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="40.35" spans="1:3">
+    <row r="14" ht="53.55" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -1574,7 +1571,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="53.55" spans="1:3">
+    <row r="16" ht="40.35" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>45</v>
       </c>
@@ -1585,16 +1582,10 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" ht="53.55" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>50</v>
-      </c>
+    <row r="17" spans="1:3">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -1606,14 +1597,13 @@
     <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg"/>
     <hyperlink ref="C8" r:id="rId7" display="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg" tooltip="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg"/>
     <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81MKKCAmRgL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C11" r:id="rId10" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
-    <hyperlink ref="C12" r:id="rId11" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C13" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
-    <hyperlink ref="C14" r:id="rId13" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
-    <hyperlink ref="C15" r:id="rId14" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
-    <hyperlink ref="C16" r:id="rId15" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C17" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1690490514i/165940202.jpg"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
+    <hyperlink ref="C12" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
+    <hyperlink ref="C13" r:id="rId12" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
+    <hyperlink ref="C14" r:id="rId13" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
+    <hyperlink ref="C15" r:id="rId14" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C16" r:id="rId15" display="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
   <si>
     <t>Title</t>
   </si>
@@ -38,139 +38,130 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>Taheren Mafi</t>
-  </si>
-  <si>
-    <t>This Woven Kingdom</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg</t>
+    <t>The Fifth Season</t>
+  </si>
+  <si>
+    <t>N. K. Jemisin</t>
+  </si>
+  <si>
+    <t>https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg</t>
+  </si>
+  <si>
+    <t>A River Enchanted</t>
   </si>
   <si>
     <t>Rebecca Ross</t>
   </si>
   <si>
-    <t>Wild Reverence</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg</t>
+    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
+  </si>
+  <si>
+    <t>The Bloody Branch</t>
   </si>
   <si>
     <t>Brigid Lowe</t>
   </si>
   <si>
-    <t>The Bloody Branch</t>
-  </si>
-  <si>
     <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
   </si>
   <si>
+    <t>Blood on Her Tongue</t>
+  </si>
+  <si>
+    <t>Johanna van Veen</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
+  </si>
+  <si>
+    <t>Jade Fire Gold</t>
+  </si>
+  <si>
     <t>June CL Tan</t>
   </si>
   <si>
-    <t>Jade Fire Gold</t>
-  </si>
-  <si>
     <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
   </si>
   <si>
+    <t>His Majesty's Dragon</t>
+  </si>
+  <si>
     <t>Naomi Novik</t>
   </si>
   <si>
-    <t>His Majesty's Dragon</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg</t>
   </si>
   <si>
-    <t>Robert Jackson Bennet</t>
-  </si>
-  <si>
-    <t>The Tainted Cup</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>Alix E. Harrow</t>
-  </si>
-  <si>
-    <t>The Everlasting</t>
-  </si>
-  <si>
-    <t>https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg</t>
+    <t>A Stage Set for Villains</t>
+  </si>
+  <si>
+    <t>Shannon J. Spann</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>The Second Death of Locke</t>
   </si>
   <si>
     <t>V. L. Bovalino</t>
   </si>
   <si>
-    <t>The Second Death of Locke</t>
-  </si>
-  <si>
     <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
   </si>
   <si>
-    <t>N. K. Jemisin</t>
-  </si>
-  <si>
-    <t>The Fifth Season</t>
-  </si>
-  <si>
-    <t>https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg</t>
+    <t>Smoke and Scar</t>
+  </si>
+  <si>
+    <t>Gretchen Powell</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
+  </si>
+  <si>
+    <t>The Wolf King</t>
   </si>
   <si>
     <t>Lauren Palphreyman</t>
   </si>
   <si>
-    <t>The Wolf King</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
   </si>
   <si>
-    <t>Gretchen Powell</t>
-  </si>
-  <si>
-    <t>Smoke and Scar</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
+  </si>
+  <si>
+    <t>Son of the morning</t>
   </si>
   <si>
     <t>Awaeke Emezi</t>
   </si>
   <si>
-    <t>Son of the morning</t>
-  </si>
-  <si>
     <t>https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg</t>
   </si>
   <si>
+    <t>The Adventures of Amina Al-Sirafi</t>
+  </si>
+  <si>
     <t>S A Chakraborty</t>
   </si>
   <si>
-    <t>The Adventures of Amina Al-Sirafi</t>
-  </si>
-  <si>
     <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10</t>
   </si>
   <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
-    <t>The Scattered Bones</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
-  </si>
-  <si>
-    <t>Shannon J. Spann</t>
-  </si>
-  <si>
-    <t>A Stage Set for Villains</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg</t>
+    <t>House of Earth and Blood</t>
+  </si>
+  <si>
+    <t>Sarah J Mass</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg</t>
   </si>
 </sst>
 </file>
@@ -372,13 +363,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -850,13 +841,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1417,7 +1408,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="53.55" spans="1:3">
+    <row r="2" ht="40.35" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1429,13 +1420,13 @@
       </c>
     </row>
     <row r="3" ht="40.35" spans="1:3">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
@@ -1446,51 +1437,51 @@
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="53.55" spans="1:3">
+    <row r="5" ht="40.35" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="27.15" spans="1:3">
+    <row r="6" ht="53.55" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="5" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="40.35" spans="1:3">
+    <row r="7" ht="27.15" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="53.55" spans="1:3">
+    <row r="8" ht="40.35" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1501,11 +1492,11 @@
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="40.35" spans="1:3">
+    <row r="10" ht="53.55" spans="1:3">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1523,7 +1514,7 @@
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1534,7 +1525,7 @@
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1545,7 +1536,7 @@
       <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1556,7 +1547,7 @@
       <c r="B14" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1567,43 +1558,36 @@
       <c r="B15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="5" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="16" ht="40.35" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+    <row r="16" ht="15.15" spans="1:3">
+      <c r="A16" s="6"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="7"/>
+    </row>
+    <row r="17" ht="15.15" spans="1:3">
       <c r="A17" s="6"/>
       <c r="B17" s="6"/>
       <c r="C17" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634235371i/56554281.jpg"/>
-    <hyperlink ref="C3" r:id="rId2" display="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg" tooltip="https://media.s-bol.com/YL0J0pDW5B4W/KOz0QJx/767x1200.jpg"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
     <hyperlink ref="C4" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg"/>
-    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/817taI05uEL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C8" r:id="rId7" display="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg" tooltip="https://ik.imagekit.io/panmac/tr:f-auto,di-placeholder_portrait_aMjPtD9YZ.jpg,w-270/edition/9781529061185.jpg"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
+    <hyperlink ref="C7" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg"/>
     <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C10" r:id="rId9" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
     <hyperlink ref="C11" r:id="rId10" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C12" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
+    <hyperlink ref="C12" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
     <hyperlink ref="C13" r:id="rId12" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
     <hyperlink ref="C14" r:id="rId13" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
-    <hyperlink ref="C15" r:id="rId14" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C16" r:id="rId15" display="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg"/>
+    <hyperlink ref="C15" r:id="rId14" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
   <si>
     <t>Title</t>
   </si>
@@ -38,130 +38,121 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>The Fifth Season</t>
-  </si>
-  <si>
-    <t>N. K. Jemisin</t>
-  </si>
-  <si>
-    <t>https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg</t>
-  </si>
-  <si>
-    <t>A River Enchanted</t>
-  </si>
-  <si>
-    <t>Rebecca Ross</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
-  </si>
-  <si>
-    <t>The Bloody Branch</t>
-  </si>
-  <si>
-    <t>Brigid Lowe</t>
-  </si>
-  <si>
-    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
-  </si>
-  <si>
-    <t>Blood on Her Tongue</t>
-  </si>
-  <si>
-    <t>Johanna van Veen</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
-  </si>
-  <si>
-    <t>Jade Fire Gold</t>
-  </si>
-  <si>
-    <t>June CL Tan</t>
-  </si>
-  <si>
-    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
-  </si>
-  <si>
-    <t>His Majesty's Dragon</t>
-  </si>
-  <si>
-    <t>Naomi Novik</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg</t>
-  </si>
-  <si>
-    <t>A Stage Set for Villains</t>
-  </si>
-  <si>
-    <t>Shannon J. Spann</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>The Second Death of Locke</t>
-  </si>
-  <si>
-    <t>V. L. Bovalino</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>Smoke and Scar</t>
-  </si>
-  <si>
-    <t>Gretchen Powell</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg</t>
-  </si>
-  <si>
-    <t>The Wolf King</t>
-  </si>
-  <si>
-    <t>Lauren Palphreyman</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
-  </si>
-  <si>
-    <t>The Scattered Bones</t>
-  </si>
-  <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
-  </si>
-  <si>
-    <t>Son of the morning</t>
-  </si>
-  <si>
-    <t>Awaeke Emezi</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg</t>
-  </si>
-  <si>
-    <t>The Adventures of Amina Al-Sirafi</t>
-  </si>
-  <si>
-    <t>S A Chakraborty</t>
-  </si>
-  <si>
-    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10</t>
-  </si>
-  <si>
-    <t>House of Earth and Blood</t>
-  </si>
-  <si>
-    <t>Sarah J Mass</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg</t>
+    <t>Dark Rise</t>
+  </si>
+  <si>
+    <t>C.S. Pacat</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81MP8ukrejL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>The Fate of Stars</t>
+  </si>
+  <si>
+    <t>S. D. Simper</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1586064387i/51253463.jpg</t>
+  </si>
+  <si>
+    <t>Gideon The Ninth</t>
+  </si>
+  <si>
+    <t>Tamsyn Muir</t>
+  </si>
+  <si>
+    <t>https://api.bruna.nl/images/active/carrousel/fullsize/9781250313188_front.jpg</t>
+  </si>
+  <si>
+    <t>A Taste of Gold and Iron</t>
+  </si>
+  <si>
+    <t>Alexandra Rowland</t>
+  </si>
+  <si>
+    <t>https://www.worldofbooks.com/cdn/shop/files/152909965X.jpg?v=1751086772&amp;width=493</t>
+  </si>
+  <si>
+    <t>She Who Became the Sun</t>
+  </si>
+  <si>
+    <t>Shelley Parker-Chan</t>
+  </si>
+  <si>
+    <t>https://i.gr-assets.com/images/S/compressed.photo.goodreads.com/books/1605538291l/55077538.jpg</t>
+  </si>
+  <si>
+    <t>Witching Moon</t>
+  </si>
+  <si>
+    <t>Poppy Woods</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/811ZQVN5V5L._UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>Wolfsong</t>
+  </si>
+  <si>
+    <t>TJ Klune</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/71aPojmBx3L._UF1000,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>The Final Strife</t>
+  </si>
+  <si>
+    <t>Saara Al Arifi</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1640248887i/54440543.jpg</t>
+  </si>
+  <si>
+    <t>A Marvellous Light</t>
+  </si>
+  <si>
+    <t>Freya Marske</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634067514i/53217284.jpg</t>
+  </si>
+  <si>
+    <t>The Unbroken</t>
+  </si>
+  <si>
+    <t>C. L. Clarke</t>
+  </si>
+  <si>
+    <t>https://i.gr-assets.com/images/S/compressed.photo.goodreads.com/books/1595284077l/54467051.jpg</t>
+  </si>
+  <si>
+    <t>Fable for the End of the World</t>
+  </si>
+  <si>
+    <t>Ava Reid</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1732371159i/209594872.jpg</t>
+  </si>
+  <si>
+    <t>You Should Be So Lucky</t>
+  </si>
+  <si>
+    <t>Cat Sebastian</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1706544152i/196774347.jpg</t>
+  </si>
+  <si>
+    <t>Sorcery and Small Magics</t>
+  </si>
+  <si>
+    <t>Maiga Doocy</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1709148725i/199826249.jpg</t>
   </si>
 </sst>
 </file>
@@ -204,9 +195,10 @@
       <charset val="134"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
       <color rgb="FF1E1915"/>
-      <name val="Arial"/>
+      <name val="Copernicus"/>
       <charset val="134"/>
     </font>
     <font>
@@ -354,18 +346,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -707,7 +693,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -731,16 +717,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -749,89 +735,89 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -841,19 +827,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1389,7 +1369,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
@@ -1419,8 +1399,8 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="40.35" spans="1:3">
-      <c r="A3" s="4" t="s">
+    <row r="3" ht="53.55" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
@@ -1430,7 +1410,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="40.35" spans="1:3">
+    <row r="4" ht="27.15" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1448,7 +1428,7 @@
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1459,18 +1439,18 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="27.15" spans="1:3">
+    <row r="7" ht="40.35" spans="1:3">
       <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
@@ -1481,18 +1461,18 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="40.35" spans="1:3">
+    <row r="9" ht="53.55" spans="1:3">
       <c r="A9" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1503,11 +1483,11 @@
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="40.35" spans="1:3">
+    <row r="11" ht="53.55" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
@@ -1525,22 +1505,22 @@
       <c r="B12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" ht="40.35" spans="1:3">
+    <row r="13" ht="53.55" spans="1:3">
       <c r="A13" s="2" t="s">
         <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="14" ht="53.55" spans="1:3">
+    <row r="14" ht="58.35" spans="1:3">
       <c r="A14" s="2" t="s">
         <v>39</v>
       </c>
@@ -1550,44 +1530,10 @@
       <c r="C14" s="5" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="15" ht="53.55" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="16" ht="15.15" spans="1:3">
-      <c r="A16" s="6"/>
-      <c r="B16" s="6"/>
-      <c r="C16" s="7"/>
-    </row>
-    <row r="17" ht="15.15" spans="1:3">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="7"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1" display="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg" tooltip="https://nkjemisin.com/wp-content/uploads/2013/09/Jemisin_FifthSeason-TP.jpg"/>
-    <hyperlink ref="C3" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
-    <hyperlink ref="C4" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
-    <hyperlink ref="C7" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/e/e2/Hmsdragon.jpg"/>
-    <hyperlink ref="C8" r:id="rId7" display="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/71D0LvsRYNL._UF1000,1000_QL80_.jpg"/>
-    <hyperlink ref="C9" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C10" r:id="rId9" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1735223143i/221866459.jpg"/>
-    <hyperlink ref="C11" r:id="rId10" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C12" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C13" r:id="rId12" display="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg" tooltip="https://media.s-bol.com/7ZEXzNWR9llj/mwjmkQr/546x840.jpg"/>
-    <hyperlink ref="C14" r:id="rId13" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTaGkpCJ9Yc_EYLHWdv-FxadI9qyYSCvpB_G57XxblwTw&amp;s=10"/>
-    <hyperlink ref="C15" r:id="rId14" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1559142847i/44778083.jpg"/>
+    <hyperlink ref="C14" r:id="rId1" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1709148725i/199826249.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Title</t>
   </si>
@@ -38,121 +38,154 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>Dark Rise</t>
-  </si>
-  <si>
-    <t>C.S. Pacat</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81MP8ukrejL._AC_UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>The Fate of Stars</t>
-  </si>
-  <si>
-    <t>S. D. Simper</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1586064387i/51253463.jpg</t>
-  </si>
-  <si>
-    <t>Gideon The Ninth</t>
-  </si>
-  <si>
-    <t>Tamsyn Muir</t>
-  </si>
-  <si>
-    <t>https://api.bruna.nl/images/active/carrousel/fullsize/9781250313188_front.jpg</t>
-  </si>
-  <si>
-    <t>A Taste of Gold and Iron</t>
-  </si>
-  <si>
-    <t>Alexandra Rowland</t>
-  </si>
-  <si>
-    <t>https://www.worldofbooks.com/cdn/shop/files/152909965X.jpg?v=1751086772&amp;width=493</t>
-  </si>
-  <si>
-    <t>She Who Became the Sun</t>
-  </si>
-  <si>
-    <t>Shelley Parker-Chan</t>
-  </si>
-  <si>
-    <t>https://i.gr-assets.com/images/S/compressed.photo.goodreads.com/books/1605538291l/55077538.jpg</t>
-  </si>
-  <si>
-    <t>Witching Moon</t>
-  </si>
-  <si>
-    <t>Poppy Woods</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/811ZQVN5V5L._UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>Wolfsong</t>
-  </si>
-  <si>
-    <t>TJ Klune</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/71aPojmBx3L._UF1000,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>The Final Strife</t>
-  </si>
-  <si>
-    <t>Saara Al Arifi</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1640248887i/54440543.jpg</t>
-  </si>
-  <si>
-    <t>A Marvellous Light</t>
-  </si>
-  <si>
-    <t>Freya Marske</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1634067514i/53217284.jpg</t>
-  </si>
-  <si>
-    <t>The Unbroken</t>
-  </si>
-  <si>
-    <t>C. L. Clarke</t>
-  </si>
-  <si>
-    <t>https://i.gr-assets.com/images/S/compressed.photo.goodreads.com/books/1595284077l/54467051.jpg</t>
-  </si>
-  <si>
-    <t>Fable for the End of the World</t>
-  </si>
-  <si>
-    <t>Ava Reid</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1732371159i/209594872.jpg</t>
-  </si>
-  <si>
-    <t>You Should Be So Lucky</t>
-  </si>
-  <si>
-    <t>Cat Sebastian</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1706544152i/196774347.jpg</t>
-  </si>
-  <si>
-    <t>Sorcery and Small Magics</t>
-  </si>
-  <si>
-    <t>Maiga Doocy</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1709148725i/199826249.jpg</t>
+    <t>BitterThorn</t>
+  </si>
+  <si>
+    <t>Kat Dunn</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg</t>
+  </si>
+  <si>
+    <t>The Poison Dauther</t>
+  </si>
+  <si>
+    <t>Sheila Masterson</t>
+  </si>
+  <si>
+    <t>https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800</t>
+  </si>
+  <si>
+    <t>Lonely castle in the mirror</t>
+  </si>
+  <si>
+    <t>Mizuki Tsujimura</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg</t>
+  </si>
+  <si>
+    <t>The Wolf King</t>
+  </si>
+  <si>
+    <t>Lauren Palphreyman</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
+  </si>
+  <si>
+    <t>The Everlasting</t>
+  </si>
+  <si>
+    <t>Alix E. Harrow</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
+  </si>
+  <si>
+    <t>A River Enchanted</t>
+  </si>
+  <si>
+    <t>Rebecca Ross</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
+  </si>
+  <si>
+    <t>The Astral Library</t>
+  </si>
+  <si>
+    <t>Kate Quinn</t>
+  </si>
+  <si>
+    <t>https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg</t>
+  </si>
+  <si>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
+  </si>
+  <si>
+    <t>The Unmagical Life of Briar Jones</t>
+  </si>
+  <si>
+    <t>Lex Croucher</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg</t>
+  </si>
+  <si>
+    <t>All my rage</t>
+  </si>
+  <si>
+    <t>Sabaa Tahir</t>
+  </si>
+  <si>
+    <t>https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg</t>
+  </si>
+  <si>
+    <t>An Ember in the Ashes</t>
+  </si>
+  <si>
+    <t>https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg</t>
+  </si>
+  <si>
+    <t>The Second Death of Locke</t>
+  </si>
+  <si>
+    <t>V. L. Bovalino</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>Daggermouth</t>
+  </si>
+  <si>
+    <t>H. M. Wolfe</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>
+  </si>
+  <si>
+    <t>The Bloody Branch</t>
+  </si>
+  <si>
+    <t>Brigid Lowe</t>
+  </si>
+  <si>
+    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
+  </si>
+  <si>
+    <t>Magic Lessons (prequel to Practical Magic)</t>
+  </si>
+  <si>
+    <t>Alice Hoffman</t>
+  </si>
+  <si>
+    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
+  </si>
+  <si>
+    <t>Blood on Her Tongue</t>
+  </si>
+  <si>
+    <t>Johanna van Veen</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
+  </si>
+  <si>
+    <t>Jade Fire Gold</t>
+  </si>
+  <si>
+    <t>June CL Tan</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
   </si>
 </sst>
 </file>
@@ -195,10 +228,9 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
       <sz val="10"/>
       <color rgb="FF1E1915"/>
-      <name val="Copernicus"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -346,7 +378,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,6 +388,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -693,7 +731,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -717,16 +755,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -735,85 +773,85 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -833,7 +871,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="6" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1369,12 +1407,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
     <col min="2" max="2" width="31.5555555555556" customWidth="1"/>
     <col min="3" max="3" width="32.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.8888888888889"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.15" spans="1:3">
@@ -1388,7 +1427,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="40.35" spans="1:3">
+    <row r="2" ht="53.55" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
@@ -1410,7 +1449,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="27.15" spans="1:3">
+    <row r="4" ht="53.55" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1432,7 +1471,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="53.55" spans="1:3">
+    <row r="6" ht="27.15" spans="1:3">
       <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1444,7 +1483,7 @@
       </c>
     </row>
     <row r="7" ht="40.35" spans="1:3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
@@ -1461,7 +1500,7 @@
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1487,53 +1526,116 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="53.55" spans="1:3">
+    <row r="11" ht="40.35" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="53.55" spans="1:3">
+    <row r="12" ht="40.35" spans="1:3">
       <c r="A12" s="2" t="s">
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" ht="40.35" spans="1:3">
+      <c r="A13" s="2" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="13" ht="53.55" spans="1:3">
-      <c r="A13" s="2" t="s">
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C13" s="3" t="s">
+    </row>
+    <row r="14" ht="53.55" spans="1:3">
+      <c r="A14" s="2" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="14" ht="58.35" spans="1:3">
-      <c r="A14" s="2" t="s">
+      <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="5" t="s">
+    </row>
+    <row r="15" ht="40.35" spans="1:3">
+      <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
+      <c r="B15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" ht="27.15" spans="1:3">
+      <c r="A16" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" ht="40.35" spans="1:3">
+      <c r="A17" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" ht="53.55" spans="1:3">
+      <c r="A18" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>52</v>
+      </c>
     </row>
   </sheetData>
+  <sortState ref="A2:D18">
+    <sortCondition ref="D2"/>
+  </sortState>
   <hyperlinks>
-    <hyperlink ref="C14" r:id="rId1" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1709148725i/199826249.jpg"/>
+    <hyperlink ref="C8" r:id="rId1" display="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg"/>
+    <hyperlink ref="C7" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
+    <hyperlink ref="C15" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
+    <hyperlink ref="C17" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
+    <hyperlink ref="C18" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
+    <hyperlink ref="C16" r:id="rId6" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
+    <hyperlink ref="C5" r:id="rId7" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
+    <hyperlink ref="C13" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C6" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
+    <hyperlink ref="C9" r:id="rId10" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C4" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
+    <hyperlink ref="C10" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
+    <hyperlink ref="C2" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg"/>
+    <hyperlink ref="C11" r:id="rId14" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
+    <hyperlink ref="C12" r:id="rId15" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
+    <hyperlink ref="C14" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
+    <hyperlink ref="C3" r:id="rId17" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
   <si>
     <t>Title</t>
   </si>
@@ -38,13 +38,49 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>BitterThorn</t>
-  </si>
-  <si>
-    <t>Kat Dunn</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg</t>
+    <t>A Harvest of Hearts</t>
+  </si>
+  <si>
+    <t>Andrea Eames</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/818bxRZSLfL._UF1000,1000_QL80_FMwebp_.jpg</t>
+  </si>
+  <si>
+    <t>Your Knife, My Heart</t>
+  </si>
+  <si>
+    <t>K.M. Moronova</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg</t>
+  </si>
+  <si>
+    <t>Cruel is the light</t>
+  </si>
+  <si>
+    <t>Sophie Clark</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg</t>
+  </si>
+  <si>
+    <t>Jade Fire Gold</t>
+  </si>
+  <si>
+    <t>June CL Tan</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
+  </si>
+  <si>
+    <t>Magic Lessons (prequel to Practical Magic)</t>
+  </si>
+  <si>
+    <t>Alice Hoffman</t>
+  </si>
+  <si>
+    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
   </si>
   <si>
     <t>The Poison Dauther</t>
@@ -56,6 +92,24 @@
     <t>https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800</t>
   </si>
   <si>
+    <t>The Everlasting</t>
+  </si>
+  <si>
+    <t>Alix E. Harrow</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
+  </si>
+  <si>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
+  </si>
+  <si>
     <t>Lonely castle in the mirror</t>
   </si>
   <si>
@@ -65,51 +119,6 @@
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg</t>
   </si>
   <si>
-    <t>The Wolf King</t>
-  </si>
-  <si>
-    <t>Lauren Palphreyman</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
-  </si>
-  <si>
-    <t>The Everlasting</t>
-  </si>
-  <si>
-    <t>Alix E. Harrow</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
-  </si>
-  <si>
-    <t>A River Enchanted</t>
-  </si>
-  <si>
-    <t>Rebecca Ross</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
-  </si>
-  <si>
-    <t>The Astral Library</t>
-  </si>
-  <si>
-    <t>Kate Quinn</t>
-  </si>
-  <si>
-    <t>https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg</t>
-  </si>
-  <si>
-    <t>The Scattered Bones</t>
-  </si>
-  <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
-  </si>
-  <si>
     <t>The Unmagical Life of Briar Jones</t>
   </si>
   <si>
@@ -134,15 +143,6 @@
     <t>https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg</t>
   </si>
   <si>
-    <t>The Second Death of Locke</t>
-  </si>
-  <si>
-    <t>V. L. Bovalino</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
     <t>Daggermouth</t>
   </si>
   <si>
@@ -152,40 +152,49 @@
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>
   </si>
   <si>
-    <t>The Bloody Branch</t>
-  </si>
-  <si>
-    <t>Brigid Lowe</t>
-  </si>
-  <si>
-    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
-  </si>
-  <si>
-    <t>Magic Lessons (prequel to Practical Magic)</t>
-  </si>
-  <si>
-    <t>Alice Hoffman</t>
-  </si>
-  <si>
-    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
-  </si>
-  <si>
-    <t>Blood on Her Tongue</t>
-  </si>
-  <si>
-    <t>Johanna van Veen</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
-  </si>
-  <si>
-    <t>Jade Fire Gold</t>
-  </si>
-  <si>
-    <t>June CL Tan</t>
-  </si>
-  <si>
-    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
+    <t>The Last Wish</t>
+  </si>
+  <si>
+    <t>Andrzej Sapkowski</t>
+  </si>
+  <si>
+    <t>https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536</t>
+  </si>
+  <si>
+    <t>One Dark Window</t>
+  </si>
+  <si>
+    <t>Rachel Gillig</t>
+  </si>
+  <si>
+    <t>https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536</t>
+  </si>
+  <si>
+    <t>Girls with Bad Reputations</t>
+  </si>
+  <si>
+    <t>Xio Axelrod</t>
+  </si>
+  <si>
+    <t>https://cdn2.penguin.com.au/covers/original/9781728261997.jpg</t>
+  </si>
+  <si>
+    <t>The Gilded Ones</t>
+  </si>
+  <si>
+    <t>Namina Forma</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536</t>
+  </si>
+  <si>
+    <t>FaeBound</t>
+  </si>
+  <si>
+    <t>Saara El Arifi</t>
+  </si>
+  <si>
+    <t>https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg</t>
   </si>
 </sst>
 </file>
@@ -221,15 +230,15 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF1E1915"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1E1915"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -865,13 +874,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1407,7 +1416,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
@@ -1427,47 +1436,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="53.55" spans="1:3">
+    <row r="2" ht="40.35" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="53.55" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="40.35" spans="1:3">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="53.55" spans="1:3">
+    <row r="4" ht="40.35" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="40.35" spans="1:3">
+    <row r="5" ht="53.55" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1478,29 +1487,29 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="40.35" spans="1:3">
-      <c r="A7" s="4" t="s">
+    <row r="7" ht="53.55" spans="1:3">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="40.35" spans="1:3">
+    <row r="8" ht="27.15" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1511,7 +1520,7 @@
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1522,18 +1531,18 @@
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="40.35" spans="1:3">
+    <row r="11" ht="53.55" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1542,20 +1551,20 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" ht="40.35" spans="1:3">
       <c r="A13" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1566,52 +1575,63 @@
       <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="4" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="40.35" spans="1:3">
+    <row r="15" ht="53.55" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="27.15" spans="1:3">
+    <row r="16" ht="53.55" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C16" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" ht="40.35" spans="1:3">
+    <row r="17" ht="27.15" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C17" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" ht="53.55" spans="1:3">
+    <row r="18" ht="40.35" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="4" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="19" ht="40.35" spans="1:3">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1619,23 +1639,23 @@
     <sortCondition ref="D2"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg"/>
-    <hyperlink ref="C7" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
-    <hyperlink ref="C15" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
-    <hyperlink ref="C17" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
-    <hyperlink ref="C18" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
-    <hyperlink ref="C16" r:id="rId6" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
-    <hyperlink ref="C5" r:id="rId7" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C13" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C6" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
-    <hyperlink ref="C9" r:id="rId10" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C4" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
-    <hyperlink ref="C10" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
-    <hyperlink ref="C2" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg"/>
-    <hyperlink ref="C11" r:id="rId14" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
-    <hyperlink ref="C12" r:id="rId15" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
-    <hyperlink ref="C14" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
-    <hyperlink ref="C3" r:id="rId17" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
+    <hyperlink ref="C3" r:id="rId1" display="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg" tooltip="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg" tooltip="https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
+    <hyperlink ref="C6" r:id="rId4" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
+    <hyperlink ref="C7" r:id="rId5" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
+    <hyperlink ref="C8" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
+    <hyperlink ref="C9" r:id="rId7" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C10" r:id="rId8" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
+    <hyperlink ref="C11" r:id="rId9" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
+    <hyperlink ref="C12" r:id="rId10" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
+    <hyperlink ref="C13" r:id="rId11" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
+    <hyperlink ref="C14" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
+    <hyperlink ref="C15" r:id="rId13" display="https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536"/>
+    <hyperlink ref="C16" r:id="rId14" display="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536"/>
+    <hyperlink ref="C17" r:id="rId15" display="https://cdn2.penguin.com.au/covers/original/9781728261997.jpg" tooltip="https://cdn2.penguin.com.au/covers/original/9781728261997.jpg"/>
+    <hyperlink ref="C18" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536" tooltip="https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536"/>
+    <hyperlink ref="C19" r:id="rId17" display="https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg" tooltip="https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -146,7 +146,7 @@
     <t>Daggermouth</t>
   </si>
   <si>
-    <t>H. M. Wolfe</t>
+    <t>H. m. Wolfe</t>
   </si>
   <si>
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>

--- a/books.xlsx
+++ b/books.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
   <si>
     <t>Title</t>
   </si>
@@ -38,31 +38,145 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>A Harvest of Hearts</t>
-  </si>
-  <si>
-    <t>Andrea Eames</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/818bxRZSLfL._UF1000,1000_QL80_FMwebp_.jpg</t>
-  </si>
-  <si>
-    <t>Your Knife, My Heart</t>
-  </si>
-  <si>
-    <t>K.M. Moronova</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg</t>
-  </si>
-  <si>
-    <t>Cruel is the light</t>
-  </si>
-  <si>
-    <t>Sophie Clark</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg</t>
+    <t>BitterThorn</t>
+  </si>
+  <si>
+    <t>Kat Dunn</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg</t>
+  </si>
+  <si>
+    <t>The Poison Dauther</t>
+  </si>
+  <si>
+    <t>Sheila Masterson</t>
+  </si>
+  <si>
+    <t>https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800</t>
+  </si>
+  <si>
+    <t>Lonely castle in the mirror</t>
+  </si>
+  <si>
+    <t>Mizuki Tsujimura</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg</t>
+  </si>
+  <si>
+    <t>The Wolf King</t>
+  </si>
+  <si>
+    <t>Lauren Palphreyman</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
+  </si>
+  <si>
+    <t>The Everlasting</t>
+  </si>
+  <si>
+    <t>Alix E. Harrow</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
+  </si>
+  <si>
+    <t>A River Enchanted</t>
+  </si>
+  <si>
+    <t>Rebecca Ross</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
+  </si>
+  <si>
+    <t>The Astral Library</t>
+  </si>
+  <si>
+    <t>Kate Quinn</t>
+  </si>
+  <si>
+    <t>https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg</t>
+  </si>
+  <si>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
+  </si>
+  <si>
+    <t>The Unmagical Life of Briar Jones</t>
+  </si>
+  <si>
+    <t>Lex Croucher</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg</t>
+  </si>
+  <si>
+    <t>All my rage</t>
+  </si>
+  <si>
+    <t>Sabaa Tahir</t>
+  </si>
+  <si>
+    <t>https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg</t>
+  </si>
+  <si>
+    <t>An Ember in the Ashes</t>
+  </si>
+  <si>
+    <t>https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg</t>
+  </si>
+  <si>
+    <t>The Second Death of Locke</t>
+  </si>
+  <si>
+    <t>V. L. Bovalino</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
+  </si>
+  <si>
+    <t>Daggermouth</t>
+  </si>
+  <si>
+    <t>H. M. Wolfe</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>
+  </si>
+  <si>
+    <t>The Bloody Branch</t>
+  </si>
+  <si>
+    <t>Brigid Lowe</t>
+  </si>
+  <si>
+    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
+  </si>
+  <si>
+    <t>Magic Lessons (prequel to Practical Magic)</t>
+  </si>
+  <si>
+    <t>Alice Hoffman</t>
+  </si>
+  <si>
+    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
+  </si>
+  <si>
+    <t>Blood on Her Tongue</t>
+  </si>
+  <si>
+    <t>Johanna van Veen</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
   </si>
   <si>
     <t>Jade Fire Gold</t>
@@ -72,129 +186,6 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
-  </si>
-  <si>
-    <t>Magic Lessons (prequel to Practical Magic)</t>
-  </si>
-  <si>
-    <t>Alice Hoffman</t>
-  </si>
-  <si>
-    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
-  </si>
-  <si>
-    <t>The Poison Dauther</t>
-  </si>
-  <si>
-    <t>Sheila Masterson</t>
-  </si>
-  <si>
-    <t>https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800</t>
-  </si>
-  <si>
-    <t>The Everlasting</t>
-  </si>
-  <si>
-    <t>Alix E. Harrow</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
-  </si>
-  <si>
-    <t>The Scattered Bones</t>
-  </si>
-  <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
-  </si>
-  <si>
-    <t>Lonely castle in the mirror</t>
-  </si>
-  <si>
-    <t>Mizuki Tsujimura</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg</t>
-  </si>
-  <si>
-    <t>The Unmagical Life of Briar Jones</t>
-  </si>
-  <si>
-    <t>Lex Croucher</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg</t>
-  </si>
-  <si>
-    <t>All my rage</t>
-  </si>
-  <si>
-    <t>Sabaa Tahir</t>
-  </si>
-  <si>
-    <t>https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg</t>
-  </si>
-  <si>
-    <t>An Ember in the Ashes</t>
-  </si>
-  <si>
-    <t>https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg</t>
-  </si>
-  <si>
-    <t>Daggermouth</t>
-  </si>
-  <si>
-    <t>H. m. Wolfe</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>
-  </si>
-  <si>
-    <t>The Last Wish</t>
-  </si>
-  <si>
-    <t>Andrzej Sapkowski</t>
-  </si>
-  <si>
-    <t>https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536</t>
-  </si>
-  <si>
-    <t>One Dark Window</t>
-  </si>
-  <si>
-    <t>Rachel Gillig</t>
-  </si>
-  <si>
-    <t>https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536</t>
-  </si>
-  <si>
-    <t>Girls with Bad Reputations</t>
-  </si>
-  <si>
-    <t>Xio Axelrod</t>
-  </si>
-  <si>
-    <t>https://cdn2.penguin.com.au/covers/original/9781728261997.jpg</t>
-  </si>
-  <si>
-    <t>The Gilded Ones</t>
-  </si>
-  <si>
-    <t>Namina Forma</t>
-  </si>
-  <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536</t>
-  </si>
-  <si>
-    <t>FaeBound</t>
-  </si>
-  <si>
-    <t>Saara El Arifi</t>
-  </si>
-  <si>
-    <t>https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg</t>
   </si>
 </sst>
 </file>
@@ -230,15 +221,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF1E1915"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1E1915"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -874,13 +865,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1416,7 +1407,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
@@ -1436,47 +1427,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="40.35" spans="1:3">
+    <row r="2" ht="53.55" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="40.35" spans="1:3">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="53.55" spans="1:3">
+      <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" ht="40.35" spans="1:3">
+    <row r="4" ht="53.55" spans="1:3">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="53.55" spans="1:3">
+    <row r="5" ht="40.35" spans="1:3">
       <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1487,29 +1478,29 @@
       <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" ht="53.55" spans="1:3">
-      <c r="A7" s="2" t="s">
+    <row r="7" ht="40.35" spans="1:3">
+      <c r="A7" s="4" t="s">
         <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="27.15" spans="1:3">
+    <row r="8" ht="40.35" spans="1:3">
       <c r="A8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1520,7 +1511,7 @@
       <c r="B9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1531,18 +1522,18 @@
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="53.55" spans="1:3">
+    <row r="11" ht="40.35" spans="1:3">
       <c r="A11" s="2" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1551,20 +1542,20 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>34</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="13" ht="40.35" spans="1:3">
       <c r="A13" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1575,63 +1566,52 @@
       <c r="B14" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" ht="53.55" spans="1:3">
+    <row r="15" ht="40.35" spans="1:3">
       <c r="A15" s="2" t="s">
         <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="16" ht="53.55" spans="1:3">
+    <row r="16" ht="27.15" spans="1:3">
       <c r="A16" s="2" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="17" ht="27.15" spans="1:3">
+    <row r="17" ht="40.35" spans="1:3">
       <c r="A17" s="2" t="s">
         <v>47</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="18" ht="40.35" spans="1:3">
+    <row r="18" ht="53.55" spans="1:3">
       <c r="A18" s="2" t="s">
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>52</v>
-      </c>
-    </row>
-    <row r="19" ht="40.35" spans="1:3">
-      <c r="A19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1639,23 +1619,23 @@
     <sortCondition ref="D2"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C3" r:id="rId1" display="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg" tooltip="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg"/>
-    <hyperlink ref="C4" r:id="rId2" display="https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg" tooltip="https://media.s-bol.com/PLgvVR5m2En6/LgkgAMA/781x1200.jpg"/>
-    <hyperlink ref="C5" r:id="rId3" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
-    <hyperlink ref="C6" r:id="rId4" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
-    <hyperlink ref="C7" r:id="rId5" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
-    <hyperlink ref="C8" r:id="rId6" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
-    <hyperlink ref="C9" r:id="rId7" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C10" r:id="rId8" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
-    <hyperlink ref="C11" r:id="rId9" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
-    <hyperlink ref="C12" r:id="rId10" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
-    <hyperlink ref="C13" r:id="rId11" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
-    <hyperlink ref="C14" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
-    <hyperlink ref="C15" r:id="rId13" display="https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2021/04/Tweet1_Witcher_Cover.jpg?resize=996,1536"/>
-    <hyperlink ref="C16" r:id="rId14" display="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536"/>
-    <hyperlink ref="C17" r:id="rId15" display="https://cdn2.penguin.com.au/covers/original/9781728261997.jpg" tooltip="https://cdn2.penguin.com.au/covers/original/9781728261997.jpg"/>
-    <hyperlink ref="C18" r:id="rId16" display="https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536" tooltip="https://upload.wikimedia.org/wikipedia/en/7/79/The_Gilded_Ones.jpg?_=20211127213536"/>
-    <hyperlink ref="C19" r:id="rId17" display="https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg" tooltip="https://www.grimdarkmagazine.com/wp-content/uploads/2024/02/Faebound.jpg"/>
+    <hyperlink ref="C8" r:id="rId1" display="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg"/>
+    <hyperlink ref="C7" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
+    <hyperlink ref="C15" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
+    <hyperlink ref="C17" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
+    <hyperlink ref="C18" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
+    <hyperlink ref="C16" r:id="rId6" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
+    <hyperlink ref="C5" r:id="rId7" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
+    <hyperlink ref="C13" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
+    <hyperlink ref="C6" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
+    <hyperlink ref="C9" r:id="rId10" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C4" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
+    <hyperlink ref="C10" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
+    <hyperlink ref="C2" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg"/>
+    <hyperlink ref="C11" r:id="rId14" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
+    <hyperlink ref="C12" r:id="rId15" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
+    <hyperlink ref="C14" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
+    <hyperlink ref="C3" r:id="rId17" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Title</t>
   </si>
@@ -38,22 +38,31 @@
     <t>Cover</t>
   </si>
   <si>
-    <t>BitterThorn</t>
-  </si>
-  <si>
-    <t>Kat Dunn</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg</t>
-  </si>
-  <si>
-    <t>The Poison Dauther</t>
-  </si>
-  <si>
-    <t>Sheila Masterson</t>
-  </si>
-  <si>
-    <t>https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800</t>
+    <t>Your Knife, My Heart</t>
+  </si>
+  <si>
+    <t>K.M. Moronova</t>
+  </si>
+  <si>
+    <t>https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg</t>
+  </si>
+  <si>
+    <t>The Gender Game</t>
+  </si>
+  <si>
+    <t>Bella Forest</t>
+  </si>
+  <si>
+    <t>https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU</t>
+  </si>
+  <si>
+    <t>The Scattered Bones</t>
+  </si>
+  <si>
+    <t>Nicole Scarano</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
   </si>
   <si>
     <t>Lonely castle in the mirror</t>
@@ -65,127 +74,58 @@
     <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg</t>
   </si>
   <si>
-    <t>The Wolf King</t>
-  </si>
-  <si>
-    <t>Lauren Palphreyman</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg</t>
-  </si>
-  <si>
-    <t>The Everlasting</t>
+    <t>Piranesi</t>
+  </si>
+  <si>
+    <t>Susanna Clarke</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg</t>
+  </si>
+  <si>
+    <t>The Mask of Mirrors</t>
+  </si>
+  <si>
+    <t>M. A. Carrick</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>One Dark Window</t>
+  </si>
+  <si>
+    <t>Rachel Gillig</t>
+  </si>
+  <si>
+    <t>https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536</t>
+  </si>
+  <si>
+    <t>Auras of the Fallen Stars</t>
+  </si>
+  <si>
+    <t>Mara van Nacht</t>
+  </si>
+  <si>
+    <t>https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg</t>
+  </si>
+  <si>
+    <t>A language of Dragons</t>
+  </si>
+  <si>
+    <t>S.F. Williamson</t>
+  </si>
+  <si>
+    <t>https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg</t>
+  </si>
+  <si>
+    <t>The Once and Future Witches</t>
   </si>
   <si>
     <t>Alix E. Harrow</t>
   </si>
   <si>
-    <t>https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg</t>
-  </si>
-  <si>
-    <t>A River Enchanted</t>
-  </si>
-  <si>
-    <t>Rebecca Ross</t>
-  </si>
-  <si>
-    <t>https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg</t>
-  </si>
-  <si>
-    <t>The Astral Library</t>
-  </si>
-  <si>
-    <t>Kate Quinn</t>
-  </si>
-  <si>
-    <t>https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg</t>
-  </si>
-  <si>
-    <t>The Scattered Bones</t>
-  </si>
-  <si>
-    <t>Nicole Scarano</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg</t>
-  </si>
-  <si>
-    <t>The Unmagical Life of Briar Jones</t>
-  </si>
-  <si>
-    <t>Lex Croucher</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg</t>
-  </si>
-  <si>
-    <t>All my rage</t>
-  </si>
-  <si>
-    <t>Sabaa Tahir</t>
-  </si>
-  <si>
-    <t>https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg</t>
-  </si>
-  <si>
-    <t>An Ember in the Ashes</t>
-  </si>
-  <si>
-    <t>https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg</t>
-  </si>
-  <si>
-    <t>The Second Death of Locke</t>
-  </si>
-  <si>
-    <t>V. L. Bovalino</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg</t>
-  </si>
-  <si>
-    <t>Daggermouth</t>
-  </si>
-  <si>
-    <t>H. M. Wolfe</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg</t>
-  </si>
-  <si>
-    <t>The Bloody Branch</t>
-  </si>
-  <si>
-    <t>Brigid Lowe</t>
-  </si>
-  <si>
-    <t>https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg</t>
-  </si>
-  <si>
-    <t>Magic Lessons (prequel to Practical Magic)</t>
-  </si>
-  <si>
-    <t>Alice Hoffman</t>
-  </si>
-  <si>
-    <t>https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550</t>
-  </si>
-  <si>
-    <t>Blood on Her Tongue</t>
-  </si>
-  <si>
-    <t>Johanna van Veen</t>
-  </si>
-  <si>
-    <t>https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg</t>
-  </si>
-  <si>
-    <t>Jade Fire Gold</t>
-  </si>
-  <si>
-    <t>June CL Tan</t>
-  </si>
-  <si>
-    <t>https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg</t>
+    <t>https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10</t>
   </si>
 </sst>
 </file>
@@ -216,6 +156,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF1E1915"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <charset val="134"/>
@@ -224,12 +170,6 @@
       <u/>
       <sz val="10"/>
       <color rgb="FF1155CC"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1E1915"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -862,16 +802,16 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -887,7 +827,7 @@
     <cellStyle name="Note" xfId="8" builtinId="10"/>
     <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
     <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
     <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
     <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
     <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
@@ -1407,7 +1347,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="34.7777777777778" customWidth="1"/>
@@ -1427,215 +1367,171 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" ht="53.55" spans="1:3">
+    <row r="2" ht="40.35" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="53.55" spans="1:3">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="66.75" spans="1:3">
+      <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" ht="53.55" spans="1:3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="40.35" spans="1:3">
-      <c r="A5" s="2" t="s">
+    <row r="5" ht="53.55" spans="1:3">
+      <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" ht="27.15" spans="1:3">
-      <c r="A6" s="2" t="s">
+    <row r="6" ht="53.55" spans="1:3">
+      <c r="A6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" ht="40.35" spans="1:3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" ht="40.35" spans="1:3">
-      <c r="A8" s="2" t="s">
+    <row r="8" ht="53.55" spans="1:3">
+      <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="53.55" spans="1:3">
-      <c r="A9" s="2" t="s">
+    <row r="9" ht="40.35" spans="1:3">
+      <c r="A9" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" ht="53.55" spans="1:3">
-      <c r="A10" s="2" t="s">
+    <row r="10" ht="40.35" spans="1:3">
+      <c r="A10" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" ht="40.35" spans="1:3">
-      <c r="A11" s="2" t="s">
+    <row r="11" ht="53.55" spans="1:3">
+      <c r="A11" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="12" ht="40.35" spans="1:3">
-      <c r="A12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" ht="40.35" spans="1:3">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" ht="53.55" spans="1:3">
-      <c r="A14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" ht="40.35" spans="1:3">
-      <c r="A15" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="16" ht="27.15" spans="1:3">
-      <c r="A16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="17" ht="40.35" spans="1:3">
-      <c r="A17" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="18" ht="53.55" spans="1:3">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>52</v>
-      </c>
+    <row r="12" ht="15.15" spans="1:3">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="5"/>
+    </row>
+    <row r="13" ht="15.15" spans="1:3">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="5"/>
+    </row>
+    <row r="14" ht="15.15" spans="1:3">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="4"/>
+    </row>
+    <row r="15" ht="15.15" spans="1:3">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="4"/>
+    </row>
+    <row r="16" ht="15.15" spans="1:3">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="4"/>
+    </row>
+    <row r="17" ht="15.15" spans="1:3">
+      <c r="A17" s="3"/>
+      <c r="B17" s="3"/>
+      <c r="C17" s="4"/>
+    </row>
+    <row r="18" ht="15.15" spans="1:3">
+      <c r="A18" s="3"/>
+      <c r="B18" s="3"/>
+      <c r="C18" s="4"/>
+    </row>
+    <row r="19" ht="15.15" spans="1:3">
+      <c r="A19" s="3"/>
+      <c r="B19" s="3"/>
+      <c r="C19" s="4"/>
     </row>
   </sheetData>
   <sortState ref="A2:D18">
     <sortCondition ref="D2"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="C8" r:id="rId1" display="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/698c5cb83fe5f15a29977a17.jpg"/>
-    <hyperlink ref="C7" r:id="rId2" display="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg" tooltip="https://media.s-bol.com/7wBmX8YN5pj8/pJnJny/550x823.jpg"/>
-    <hyperlink ref="C15" r:id="rId3" display="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg" tooltip="https://cdn.penguin.co.uk/dam-assets/books/9781787305250/9781787305250-jacket-large.jpg"/>
-    <hyperlink ref="C17" r:id="rId4" display="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg" tooltip="https://m.media-amazon.com/images/I/41netiV9O6L._SY445_SX342_QL70_FMwebp_.jpg"/>
-    <hyperlink ref="C18" r:id="rId5" display="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg" tooltip="https://images.squarespace-cdn.com/content/v1/5fa4660bb109d3087785cca0/27525d3a-e30b-4d08-ae30-719f400c4a0e/JFG_OC.jpg"/>
-    <hyperlink ref="C16" r:id="rId6" display="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550" tooltip="https://thefrida.nl/cdn/shop/files/57111448.jpg?v=1768476328&amp;width=550"/>
-    <hyperlink ref="C5" r:id="rId7" display="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg" tooltip="https://media.s-bol.com/KqEy5EnjP52J/58KrVGX/780x1200.jpg"/>
-    <hyperlink ref="C13" r:id="rId8" display="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg" tooltip="https://m.media-amazon.com/images/I/81XCo+49lBL._AC_UF894,1000_QL80_.jpg"/>
-    <hyperlink ref="C6" r:id="rId9" display="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg" tooltip="https://upload.wikimedia.org/wikipedia/en/f/f0/The_Everlasting_cover.jpg"/>
-    <hyperlink ref="C9" r:id="rId10" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C4" r:id="rId11" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
-    <hyperlink ref="C10" r:id="rId12" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1762544962i/209774035.jpg"/>
-    <hyperlink ref="C2" r:id="rId13" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1674760822i/61688564.jpg"/>
-    <hyperlink ref="C11" r:id="rId14" display="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2021/11/ALL-MY-RAGE.jpg"/>
-    <hyperlink ref="C12" r:id="rId15" display="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg" tooltip="https://sabaatahir.com/wp-content/uploads/2024/09/Ember_in_the_Ashes.jpg"/>
-    <hyperlink ref="C14" r:id="rId16" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1774961536i/247928235.jpg"/>
-    <hyperlink ref="C3" r:id="rId17" display="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800" tooltip="https://www.themysteriousbookcase.com/cdn/shop/files/81ovio4wq-L._SL1500.jpg?v=1775058942&amp;width=800"/>
+    <hyperlink ref="C2" r:id="rId1" display="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg" tooltip="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg"/>
+    <hyperlink ref="C3" r:id="rId2" display="https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU" tooltip="https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU"/>
+    <hyperlink ref="C4" r:id="rId3" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
+    <hyperlink ref="C6" r:id="rId5" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg"/>
+    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg" tooltip="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg"/>
+    <hyperlink ref="C8" r:id="rId7" display="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536"/>
+    <hyperlink ref="C9" r:id="rId8" display="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg"/>
+    <hyperlink ref="C10" r:id="rId9" display="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg" tooltip="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg"/>
+    <hyperlink ref="C11" r:id="rId10" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/books.xlsx
+++ b/books.xlsx
@@ -53,7 +53,7 @@
     <t>Bella Forest</t>
   </si>
   <si>
-    <t>https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU</t>
+    <t>https://bellaforrest.com/cdn/shop/products/9780998299211_grande.jpg?v=1704119535</t>
   </si>
   <si>
     <t>The Scattered Bones</t>
@@ -1378,7 +1378,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" ht="66.75" spans="1:3">
+    <row r="3" ht="40.35" spans="1:3">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -1523,15 +1523,14 @@
   </sortState>
   <hyperlinks>
     <hyperlink ref="C2" r:id="rId1" display="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg" tooltip="https://media.s-bol.com/wLVYWzVEXrVJ/583lYxA/945x1200.jpg"/>
-    <hyperlink ref="C3" r:id="rId2" display="https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU" tooltip="https://bellaforrest.com/collections/the-gender-game?srsltid=AfmBOorvrI3bIXaUX3QMYQGtkWlLcfS9hI5wZK84-8KRp7eroJSDZ8rU"/>
-    <hyperlink ref="C4" r:id="rId3" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
-    <hyperlink ref="C5" r:id="rId4" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
-    <hyperlink ref="C6" r:id="rId5" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg"/>
-    <hyperlink ref="C7" r:id="rId6" display="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg" tooltip="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg"/>
-    <hyperlink ref="C8" r:id="rId7" display="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536"/>
-    <hyperlink ref="C9" r:id="rId8" display="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg"/>
-    <hyperlink ref="C10" r:id="rId9" display="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg" tooltip="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg"/>
-    <hyperlink ref="C11" r:id="rId10" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10"/>
+    <hyperlink ref="C4" r:id="rId2" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1692132539i/162728103.jpg"/>
+    <hyperlink ref="C5" r:id="rId3" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1596014992i/54633167.jpg"/>
+    <hyperlink ref="C6" r:id="rId4" display="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg" tooltip="https://m.media-amazon.com/images/S/compressed.photo.goodreads.com/books/1773750050i/50202953.jpg"/>
+    <hyperlink ref="C7" r:id="rId5" display="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg" tooltip="https://m.media-amazon.com/images/I/8113lwYQLtL._AC_SL1500_.jpg"/>
+    <hyperlink ref="C8" r:id="rId6" display="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536" tooltip="https://www.hachettebookgroup.com/wp-content/uploads/2026/02/9780316312486.jpg?resize=1021,1536"/>
+    <hyperlink ref="C9" r:id="rId7" display="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg" tooltip="https://s3.amazonaws.com/romance.io/books/large/69282eb47402b702d69add6b.jpg"/>
+    <hyperlink ref="C10" r:id="rId8" display="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg" tooltip="https://somanypages.nl/wp-content/uploads/2025/01/A-language-of-dragons.jpg"/>
+    <hyperlink ref="C11" r:id="rId9" display="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10" tooltip="https://encrypted-tbn0.gstatic.com/images?q=tbn:ANd9GcTyS1AAQtPlT83JTcu9joW73Y162Uuaufxa_cJUkFnvuQ&amp;s=10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
